--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20250201_20250801.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20250201_20250801.xlsx
@@ -657,37 +657,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57.37704918032787</v>
+        <v>56.55737704918032</v>
       </c>
       <c r="C6" t="n">
-        <v>42.62295081967213</v>
+        <v>43.44262295081967</v>
       </c>
       <c r="D6" t="n">
-        <v>41.49131116019083</v>
+        <v>43.21105032283729</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>INE463V01026</t>
+          <t>INE206F01022</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>-14.75409836065574</v>
+        <v>-13.11475409836066</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>2645.6</v>
+        <v>555.25</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -701,37 +701,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AIIL</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56.55737704918032</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="C7" t="n">
-        <v>43.44262295081967</v>
+        <v>42.62295081967213</v>
       </c>
       <c r="D7" t="n">
-        <v>43.21105032283729</v>
+        <v>41.49131116019083</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>INE206F01022</t>
+          <t>INE463V01026</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>-13.11475409836066</v>
+        <v>-14.75409836065574</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
         <v>36</v>
       </c>
       <c r="J7" t="n">
-        <v>555.25</v>
+        <v>2645.6</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
         <v>-16.39344262295081</v>
@@ -816,7 +816,7 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J9" t="n">
         <v>2064.8</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
         <v>-18.0327868852459</v>
@@ -860,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J10" t="n">
         <v>1501.4</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
         <v>-13.11475409836066</v>
@@ -992,7 +992,7 @@
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J13" t="n">
         <v>756</v>
@@ -1141,37 +1141,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53.27868852459017</v>
+        <v>54.09836065573771</v>
       </c>
       <c r="C17" t="n">
-        <v>46.72131147540984</v>
+        <v>45.90163934426229</v>
       </c>
       <c r="D17" t="n">
-        <v>44.32230202724583</v>
+        <v>40.14562966666999</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>INE935A01035</t>
+          <t>INE982J01020</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.557377049180324</v>
+        <v>-8.196721311475414</v>
       </c>
       <c r="H17" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="I17" t="n">
         <v>92</v>
       </c>
       <c r="J17" t="n">
-        <v>2134.1</v>
+        <v>1089.35</v>
       </c>
       <c r="K17" t="n">
         <v>16</v>
@@ -1185,37 +1185,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.09836065573771</v>
+        <v>53.27868852459017</v>
       </c>
       <c r="C18" t="n">
-        <v>45.90163934426229</v>
+        <v>46.72131147540984</v>
       </c>
       <c r="D18" t="n">
-        <v>40.14562966666999</v>
+        <v>44.32230202724583</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>INE982J01020</t>
+          <t>INE935A01035</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.196721311475414</v>
+        <v>-6.557377049180324</v>
       </c>
       <c r="H18" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I18" t="n">
         <v>92</v>
       </c>
       <c r="J18" t="n">
-        <v>1089.35</v>
+        <v>2134.1</v>
       </c>
       <c r="K18" t="n">
         <v>17</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
         <v>-9.836065573770497</v>
@@ -1256,7 +1256,7 @@
         <v>38</v>
       </c>
       <c r="I19" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J19" t="n">
         <v>5910.5</v>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
         <v>-9.836065573770497</v>
@@ -1300,7 +1300,7 @@
         <v>34</v>
       </c>
       <c r="I20" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J20" t="n">
         <v>2640.9</v>
@@ -1317,37 +1317,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>56.55737704918032</v>
+        <v>53.27868852459017</v>
       </c>
       <c r="C21" t="n">
-        <v>42.62295081967213</v>
+        <v>45.90163934426229</v>
       </c>
       <c r="D21" t="n">
-        <v>25.82777985793632</v>
+        <v>38.84737007595951</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>INE040A01034</t>
+          <t>INE758E01017</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>-13.9344262295082</v>
+        <v>-7.377049180327873</v>
       </c>
       <c r="H21" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="I21" t="n">
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>1009.1</v>
+        <v>329.25</v>
       </c>
       <c r="K21" t="n">
         <v>20</v>
